--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/4565-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/4565-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88A037B5-5FFC-468B-8B44-AE86F7F387D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6E901CC-29A7-459F-8A98-5F01E08E1058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{DF76EFEB-AFA1-410C-8BB4-866A5A015A74}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{FD7194E1-245F-41D3-8E43-0EC303BE92DF}"/>
   </bookViews>
   <sheets>
     <sheet name="4565-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1511,24 +1511,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28456181-5111-4760-91A0-0575A2F0F6D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D5762F3-A122-4A1B-9427-75F8C10DE96B}">
   <dimension ref="A1:X16"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1562,7 +1561,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1598,7 +1597,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1650,7 +1649,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1718,7 +1717,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1790,7 +1789,7 @@
         <v>6.34</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1862,7 +1861,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="41"/>
       <c r="B7" s="42"/>
       <c r="C7" s="17" t="s">
@@ -1890,7 +1889,7 @@
       <c r="W7" s="48"/>
       <c r="X7" s="44"/>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2022</v>
       </c>
@@ -1962,7 +1961,7 @@
         <v>6.38</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="49">
         <v>2021</v>
       </c>
@@ -2034,7 +2033,7 @@
         <v>8.17</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2020</v>
       </c>
@@ -2106,7 +2105,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="49">
         <v>2019</v>
       </c>
@@ -2178,7 +2177,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2018</v>
       </c>
@@ -2250,7 +2249,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="49">
         <v>2017</v>
       </c>
@@ -2322,7 +2321,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="51">
         <v>2016</v>
       </c>
@@ -2394,7 +2393,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="53"/>
       <c r="B15" s="54"/>
       <c r="C15" s="20" t="s">
@@ -2422,7 +2421,7 @@
       <c r="W15" s="60"/>
       <c r="X15" s="56"/>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="49" t="s">
         <v>39</v>
       </c>
